--- a/Piaui/2026/ResultadosTRI_3EM_MT/Simulado_I/EstItens_3EM_MT_S1.xlsx
+++ b/Piaui/2026/ResultadosTRI_3EM_MT/Simulado_I/EstItens_3EM_MT_S1.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t xml:space="preserve">007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">008</t>
   </si>
   <si>
     <t xml:space="preserve">009</t>
@@ -476,7 +473,7 @@
         <v>1.01438425</v>
       </c>
       <c r="C2" t="n">
-        <v>0.968468</v>
+        <v>0.968468000000003</v>
       </c>
       <c r="D2" t="n">
         <v>0.020287685</v>
@@ -485,7 +482,7 @@
         <v>298.4234</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0234630000000001</v>
+        <v>0.0234629999999999</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
@@ -496,10 +493,10 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5384771</v>
+        <v>0.538477099999999</v>
       </c>
       <c r="C3" t="n">
-        <v>3.985406</v>
+        <v>3.98540600000001</v>
       </c>
       <c r="D3" t="n">
         <v>0.010769542</v>
@@ -508,7 +505,7 @@
         <v>449.2703</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0732108400000002</v>
+        <v>0.0732108399999999</v>
       </c>
       <c r="G3" t="s">
         <v>8</v>
@@ -519,19 +516,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>1.49571997253823</v>
+        <v>1.27825583453567</v>
       </c>
       <c r="C4" t="n">
-        <v>3.24781123310278</v>
+        <v>3.72977488271628</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0299143994507647</v>
+        <v>0.0255651166907134</v>
       </c>
       <c r="E4" t="n">
-        <v>412.390561655139</v>
+        <v>436.488744135814</v>
       </c>
       <c r="F4" t="n">
-        <v>0.238821249233815</v>
+        <v>0.236450334784754</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
@@ -542,19 +539,19 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>1.15264635409087</v>
+        <v>1.00427691033734</v>
       </c>
       <c r="C5" t="n">
-        <v>2.73202974834962</v>
+        <v>3.11915517754481</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0230529270818174</v>
+        <v>0.0200855382067469</v>
       </c>
       <c r="E5" t="n">
-        <v>386.601487417481</v>
+        <v>405.95775887724</v>
       </c>
       <c r="F5" t="n">
-        <v>0.107810678576922</v>
+        <v>0.101594873870655</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
@@ -565,19 +562,19 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>1.79839024671001</v>
+        <v>1.57833984881459</v>
       </c>
       <c r="C6" t="n">
-        <v>2.19778182800667</v>
+        <v>2.51723882955416</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0359678049342003</v>
+        <v>0.0315667969762919</v>
       </c>
       <c r="E6" t="n">
-        <v>359.889091400334</v>
+        <v>375.861941477708</v>
       </c>
       <c r="F6" t="n">
-        <v>0.143532182108711</v>
+        <v>0.138477841650351</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -588,19 +585,19 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>2.27636655966518</v>
+        <v>2.03555049325795</v>
       </c>
       <c r="C7" t="n">
-        <v>1.89921752647194</v>
+        <v>2.18935560773444</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0455273311933036</v>
+        <v>0.0407110098651589</v>
       </c>
       <c r="E7" t="n">
-        <v>344.960876323597</v>
+        <v>359.467780386722</v>
       </c>
       <c r="F7" t="n">
-        <v>0.173799014127737</v>
+        <v>0.170306735003161</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -611,19 +608,19 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1.98377702967727</v>
+        <v>1.65996998892298</v>
       </c>
       <c r="C8" t="n">
-        <v>2.99478439148641</v>
+        <v>3.44428696974976</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0396755405935455</v>
+        <v>0.0331993997784597</v>
       </c>
       <c r="E8" t="n">
-        <v>399.73921957432</v>
+        <v>422.214348487488</v>
       </c>
       <c r="F8" t="n">
-        <v>0.134073379107508</v>
+        <v>0.13148517220229</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
@@ -634,19 +631,19 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>0.683998177122055</v>
+        <v>1.16802922637208</v>
       </c>
       <c r="C9" t="n">
-        <v>0.944868240442021</v>
+        <v>1.88821090965918</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0136799635424411</v>
+        <v>0.0233605845274416</v>
       </c>
       <c r="E9" t="n">
-        <v>297.243412022101</v>
+        <v>344.410545482959</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0563128719578938</v>
+        <v>0.112709830426179</v>
       </c>
       <c r="G9" t="s">
         <v>8</v>
@@ -657,22 +654,22 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>1.16802922637208</v>
+        <v>2.53813646894852</v>
       </c>
       <c r="C10" t="n">
-        <v>1.88821090965918</v>
+        <v>2.73576189066435</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0233605845274416</v>
+        <v>0.0507627293789704</v>
       </c>
       <c r="E10" t="n">
-        <v>344.410545482959</v>
+        <v>386.788094533217</v>
       </c>
       <c r="F10" t="n">
-        <v>0.112709830426179</v>
+        <v>0.256664692915046</v>
       </c>
       <c r="G10" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -680,19 +677,19 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>2.80598297005202</v>
+        <v>0.97316576756899</v>
       </c>
       <c r="C11" t="n">
-        <v>2.39109563007909</v>
+        <v>1.36533669131312</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0561196594010404</v>
+        <v>0.0194633153513798</v>
       </c>
       <c r="E11" t="n">
-        <v>369.554781503954</v>
+        <v>318.266834565656</v>
       </c>
       <c r="F11" t="n">
-        <v>0.257394002117577</v>
+        <v>0.120007091934637</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -703,19 +700,19 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1.06711344970948</v>
+        <v>1.77953647252648</v>
       </c>
       <c r="C12" t="n">
-        <v>1.1081675344138</v>
+        <v>1.87625413266291</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0213422689941896</v>
+        <v>0.0355907294505296</v>
       </c>
       <c r="E12" t="n">
-        <v>305.40837672069</v>
+        <v>343.812706633146</v>
       </c>
       <c r="F12" t="n">
-        <v>0.114481850070226</v>
+        <v>0.130368041209199</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
@@ -726,19 +723,19 @@
         <v>20</v>
       </c>
       <c r="B13" t="n">
-        <v>1.90518835429313</v>
+        <v>1.08409037875955</v>
       </c>
       <c r="C13" t="n">
-        <v>1.58289565718286</v>
+        <v>1.99158665783271</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0381037670858627</v>
+        <v>0.021681807575191</v>
       </c>
       <c r="E13" t="n">
-        <v>329.144782859143</v>
+        <v>349.579332891635</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1255333557085</v>
+        <v>0.118586187795713</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -749,19 +746,19 @@
         <v>21</v>
       </c>
       <c r="B14" t="n">
-        <v>1.19707001886912</v>
+        <v>0.864656101622476</v>
       </c>
       <c r="C14" t="n">
-        <v>1.69653064629389</v>
+        <v>3.27531478684193</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0239414003773824</v>
+        <v>0.0172931220324495</v>
       </c>
       <c r="E14" t="n">
-        <v>334.826532314694</v>
+        <v>413.765739342097</v>
       </c>
       <c r="F14" t="n">
-        <v>0.118342732107112</v>
+        <v>0.149217740568832</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
@@ -772,19 +769,19 @@
         <v>22</v>
       </c>
       <c r="B15" t="n">
-        <v>1.01689224832455</v>
+        <v>1.58660335375993</v>
       </c>
       <c r="C15" t="n">
-        <v>2.86425015471777</v>
+        <v>3.828365071639</v>
       </c>
       <c r="D15" t="n">
-        <v>0.020337844966491</v>
+        <v>0.0317320670751987</v>
       </c>
       <c r="E15" t="n">
-        <v>393.212507735888</v>
+        <v>441.41825358195</v>
       </c>
       <c r="F15" t="n">
-        <v>0.158065373745723</v>
+        <v>0.165681114601585</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -795,19 +792,19 @@
         <v>23</v>
       </c>
       <c r="B16" t="n">
-        <v>1.84274165364575</v>
+        <v>0.478745215985887</v>
       </c>
       <c r="C16" t="n">
-        <v>3.32939325342833</v>
+        <v>3.41892021911421</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0368548330729151</v>
+        <v>0.00957490431971774</v>
       </c>
       <c r="E16" t="n">
-        <v>416.469662671417</v>
+        <v>420.94601095571</v>
       </c>
       <c r="F16" t="n">
-        <v>0.16643587713991</v>
+        <v>0.0883300542486196</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -818,19 +815,19 @@
         <v>24</v>
       </c>
       <c r="B17" t="n">
-        <v>0.527649752206104</v>
+        <v>1.34868030267701</v>
       </c>
       <c r="C17" t="n">
-        <v>2.9422510997939</v>
+        <v>3.31778542533145</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0105529950441221</v>
+        <v>0.0269736060535403</v>
       </c>
       <c r="E17" t="n">
-        <v>397.112554989695</v>
+        <v>415.889271266572</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0830929411150078</v>
+        <v>0.244027280290688</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
@@ -841,19 +838,19 @@
         <v>25</v>
       </c>
       <c r="B18" t="n">
-        <v>1.60501742434143</v>
+        <v>1.62156198903047</v>
       </c>
       <c r="C18" t="n">
-        <v>2.88845732787593</v>
+        <v>2.83763187369344</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0321003484868285</v>
+        <v>0.0324312397806094</v>
       </c>
       <c r="E18" t="n">
-        <v>394.422866393796</v>
+        <v>391.881593684672</v>
       </c>
       <c r="F18" t="n">
-        <v>0.248057358405895</v>
+        <v>0.166576984043539</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
@@ -864,19 +861,19 @@
         <v>26</v>
       </c>
       <c r="B19" t="n">
-        <v>1.84595393409254</v>
+        <v>2.46170027267156</v>
       </c>
       <c r="C19" t="n">
-        <v>2.47962246500893</v>
+        <v>2.4054463568768</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0369190786818508</v>
+        <v>0.0492340054534311</v>
       </c>
       <c r="E19" t="n">
-        <v>373.981123250447</v>
+        <v>370.27231784384</v>
       </c>
       <c r="F19" t="n">
-        <v>0.169616369397473</v>
+        <v>0.188459040238128</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
@@ -887,19 +884,19 @@
         <v>27</v>
       </c>
       <c r="B20" t="n">
-        <v>2.81213758005362</v>
+        <v>1.79149491710978</v>
       </c>
       <c r="C20" t="n">
-        <v>2.10122290575614</v>
+        <v>2.16819183133219</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0562427516010724</v>
+        <v>0.0358298983421955</v>
       </c>
       <c r="E20" t="n">
-        <v>355.061145287807</v>
+        <v>358.40959156661</v>
       </c>
       <c r="F20" t="n">
-        <v>0.192321125988655</v>
+        <v>0.134022867321996</v>
       </c>
       <c r="G20" t="s">
         <v>11</v>
@@ -910,19 +907,19 @@
         <v>28</v>
       </c>
       <c r="B21" t="n">
-        <v>1.95163830744445</v>
+        <v>1.09957922332884</v>
       </c>
       <c r="C21" t="n">
-        <v>1.85934840042381</v>
+        <v>2.89593852746767</v>
       </c>
       <c r="D21" t="n">
-        <v>0.039032766148889</v>
+        <v>0.0219915844665768</v>
       </c>
       <c r="E21" t="n">
-        <v>342.967420021191</v>
+        <v>394.796926373384</v>
       </c>
       <c r="F21" t="n">
-        <v>0.132467436743443</v>
+        <v>0.224422000574448</v>
       </c>
       <c r="G21" t="s">
         <v>11</v>
@@ -933,19 +930,19 @@
         <v>29</v>
       </c>
       <c r="B22" t="n">
-        <v>1.24600407436677</v>
+        <v>1.76838321535747</v>
       </c>
       <c r="C22" t="n">
-        <v>2.51720523013369</v>
+        <v>2.46807820805403</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0249200814873353</v>
+        <v>0.0353676643071494</v>
       </c>
       <c r="E22" t="n">
-        <v>375.860261506684</v>
+        <v>373.403910402701</v>
       </c>
       <c r="F22" t="n">
-        <v>0.226747050951325</v>
+        <v>0.159246532165181</v>
       </c>
       <c r="G22" t="s">
         <v>11</v>
@@ -956,19 +953,19 @@
         <v>30</v>
       </c>
       <c r="B23" t="n">
-        <v>1.98121646697375</v>
+        <v>1.55444022893458</v>
       </c>
       <c r="C23" t="n">
-        <v>2.15134938066146</v>
+        <v>2.49874431048931</v>
       </c>
       <c r="D23" t="n">
-        <v>0.039624329339475</v>
+        <v>0.0310888045786916</v>
       </c>
       <c r="E23" t="n">
-        <v>357.567469033073</v>
+        <v>374.937215524465</v>
       </c>
       <c r="F23" t="n">
-        <v>0.162451003015797</v>
+        <v>0.151249326502043</v>
       </c>
       <c r="G23" t="s">
         <v>11</v>
@@ -979,19 +976,19 @@
         <v>31</v>
       </c>
       <c r="B24" t="n">
-        <v>1.73132134739972</v>
+        <v>0.269236345015944</v>
       </c>
       <c r="C24" t="n">
-        <v>2.17523169728017</v>
+        <v>4.12702385973277</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0346264269479944</v>
+        <v>0.00538472690031889</v>
       </c>
       <c r="E24" t="n">
-        <v>358.761584864008</v>
+        <v>456.351192986638</v>
       </c>
       <c r="F24" t="n">
-        <v>0.153820425323923</v>
+        <v>0.0440545277271453</v>
       </c>
       <c r="G24" t="s">
         <v>11</v>
@@ -1002,22 +999,22 @@
         <v>32</v>
       </c>
       <c r="B25" t="n">
-        <v>0.300247083831795</v>
+        <v>2.85</v>
       </c>
       <c r="C25" t="n">
-        <v>3.60018450162607</v>
+        <v>2.35786</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0060049416766359</v>
+        <v>0.057</v>
       </c>
       <c r="E25" t="n">
-        <v>430.009225081303</v>
+        <v>367.893</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0441663572344428</v>
+        <v>0.156</v>
       </c>
       <c r="G25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -1025,44 +1022,21 @@
         <v>33</v>
       </c>
       <c r="B26" t="n">
-        <v>2.85</v>
+        <v>1.40498967035606</v>
       </c>
       <c r="C26" t="n">
-        <v>2.35786</v>
+        <v>2.51399798875245</v>
       </c>
       <c r="D26" t="n">
-        <v>0.057</v>
+        <v>0.0280997934071211</v>
       </c>
       <c r="E26" t="n">
-        <v>367.893</v>
+        <v>375.699899437622</v>
       </c>
       <c r="F26" t="n">
-        <v>0.156</v>
+        <v>0.15595897164757</v>
       </c>
       <c r="G26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" t="n">
-        <v>1.5341214625056</v>
-      </c>
-      <c r="C27" t="n">
-        <v>2.18105819723049</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.030682429250112</v>
-      </c>
-      <c r="E27" t="n">
-        <v>359.052909861525</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.155858756228296</v>
-      </c>
-      <c r="G27" t="s">
         <v>11</v>
       </c>
     </row>

--- a/Piaui/2026/ResultadosTRI_3EM_MT/Simulado_I/EstItens_3EM_MT_S1.xlsx
+++ b/Piaui/2026/ResultadosTRI_3EM_MT/Simulado_I/EstItens_3EM_MT_S1.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t xml:space="preserve">007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">008</t>
   </si>
   <si>
     <t xml:space="preserve">009</t>
@@ -473,7 +476,7 @@
         <v>1.01438425</v>
       </c>
       <c r="C2" t="n">
-        <v>0.968468000000003</v>
+        <v>0.968468</v>
       </c>
       <c r="D2" t="n">
         <v>0.020287685</v>
@@ -482,7 +485,7 @@
         <v>298.4234</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0234629999999999</v>
+        <v>0.0234630000000001</v>
       </c>
       <c r="G2" t="s">
         <v>8</v>
@@ -493,10 +496,10 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>0.538477099999999</v>
+        <v>0.5384771</v>
       </c>
       <c r="C3" t="n">
-        <v>3.98540600000001</v>
+        <v>3.985406</v>
       </c>
       <c r="D3" t="n">
         <v>0.010769542</v>
@@ -505,7 +508,7 @@
         <v>449.2703</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0732108399999999</v>
+        <v>0.0732108400000002</v>
       </c>
       <c r="G3" t="s">
         <v>8</v>
@@ -516,19 +519,19 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>1.27825583453567</v>
+        <v>1.49571997253823</v>
       </c>
       <c r="C4" t="n">
-        <v>3.72977488271628</v>
+        <v>3.24781123310278</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0255651166907134</v>
+        <v>0.0299143994507647</v>
       </c>
       <c r="E4" t="n">
-        <v>436.488744135814</v>
+        <v>412.390561655139</v>
       </c>
       <c r="F4" t="n">
-        <v>0.236450334784754</v>
+        <v>0.238821249233815</v>
       </c>
       <c r="G4" t="s">
         <v>11</v>
@@ -539,19 +542,19 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>1.00427691033734</v>
+        <v>1.15264635409087</v>
       </c>
       <c r="C5" t="n">
-        <v>3.11915517754481</v>
+        <v>2.73202974834962</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0200855382067469</v>
+        <v>0.0230529270818174</v>
       </c>
       <c r="E5" t="n">
-        <v>405.95775887724</v>
+        <v>386.601487417481</v>
       </c>
       <c r="F5" t="n">
-        <v>0.101594873870655</v>
+        <v>0.107810678576922</v>
       </c>
       <c r="G5" t="s">
         <v>11</v>
@@ -562,19 +565,19 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>1.57833984881459</v>
+        <v>1.79839024671001</v>
       </c>
       <c r="C6" t="n">
-        <v>2.51723882955416</v>
+        <v>2.19778182800667</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0315667969762919</v>
+        <v>0.0359678049342003</v>
       </c>
       <c r="E6" t="n">
-        <v>375.861941477708</v>
+        <v>359.889091400334</v>
       </c>
       <c r="F6" t="n">
-        <v>0.138477841650351</v>
+        <v>0.143532182108711</v>
       </c>
       <c r="G6" t="s">
         <v>11</v>
@@ -585,19 +588,19 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>2.03555049325795</v>
+        <v>2.27636655966518</v>
       </c>
       <c r="C7" t="n">
-        <v>2.18935560773444</v>
+        <v>1.89921752647194</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0407110098651589</v>
+        <v>0.0455273311933036</v>
       </c>
       <c r="E7" t="n">
-        <v>359.467780386722</v>
+        <v>344.960876323597</v>
       </c>
       <c r="F7" t="n">
-        <v>0.170306735003161</v>
+        <v>0.173799014127737</v>
       </c>
       <c r="G7" t="s">
         <v>11</v>
@@ -608,19 +611,19 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1.65996998892298</v>
+        <v>1.98377702967727</v>
       </c>
       <c r="C8" t="n">
-        <v>3.44428696974976</v>
+        <v>2.99478439148641</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0331993997784597</v>
+        <v>0.0396755405935455</v>
       </c>
       <c r="E8" t="n">
-        <v>422.214348487488</v>
+        <v>399.73921957432</v>
       </c>
       <c r="F8" t="n">
-        <v>0.13148517220229</v>
+        <v>0.134073379107508</v>
       </c>
       <c r="G8" t="s">
         <v>11</v>
@@ -631,19 +634,19 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>1.16802922637208</v>
+        <v>0.683998177122055</v>
       </c>
       <c r="C9" t="n">
-        <v>1.88821090965918</v>
+        <v>0.944868240442021</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0233605845274416</v>
+        <v>0.0136799635424411</v>
       </c>
       <c r="E9" t="n">
-        <v>344.410545482959</v>
+        <v>297.243412022101</v>
       </c>
       <c r="F9" t="n">
-        <v>0.112709830426179</v>
+        <v>0.0563128719578938</v>
       </c>
       <c r="G9" t="s">
         <v>8</v>
@@ -654,22 +657,22 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>2.53813646894852</v>
+        <v>1.16802922637208</v>
       </c>
       <c r="C10" t="n">
-        <v>2.73576189066435</v>
+        <v>1.88821090965918</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0507627293789704</v>
+        <v>0.0233605845274416</v>
       </c>
       <c r="E10" t="n">
-        <v>386.788094533217</v>
+        <v>344.410545482959</v>
       </c>
       <c r="F10" t="n">
-        <v>0.256664692915046</v>
+        <v>0.112709830426179</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -677,19 +680,19 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>0.97316576756899</v>
+        <v>2.80598297005202</v>
       </c>
       <c r="C11" t="n">
-        <v>1.36533669131312</v>
+        <v>2.39109563007909</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0194633153513798</v>
+        <v>0.0561196594010404</v>
       </c>
       <c r="E11" t="n">
-        <v>318.266834565656</v>
+        <v>369.554781503954</v>
       </c>
       <c r="F11" t="n">
-        <v>0.120007091934637</v>
+        <v>0.257394002117577</v>
       </c>
       <c r="G11" t="s">
         <v>11</v>
@@ -700,19 +703,19 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>1.77953647252648</v>
+        <v>1.06711344970948</v>
       </c>
       <c r="C12" t="n">
-        <v>1.87625413266291</v>
+        <v>1.1081675344138</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0355907294505296</v>
+        <v>0.0213422689941896</v>
       </c>
       <c r="E12" t="n">
-        <v>343.812706633146</v>
+        <v>305.40837672069</v>
       </c>
       <c r="F12" t="n">
-        <v>0.130368041209199</v>
+        <v>0.114481850070226</v>
       </c>
       <c r="G12" t="s">
         <v>11</v>
@@ -723,19 +726,19 @@
         <v>20</v>
       </c>
       <c r="B13" t="n">
-        <v>1.08409037875955</v>
+        <v>1.90518835429313</v>
       </c>
       <c r="C13" t="n">
-        <v>1.99158665783271</v>
+        <v>1.58289565718286</v>
       </c>
       <c r="D13" t="n">
-        <v>0.021681807575191</v>
+        <v>0.0381037670858627</v>
       </c>
       <c r="E13" t="n">
-        <v>349.579332891635</v>
+        <v>329.144782859143</v>
       </c>
       <c r="F13" t="n">
-        <v>0.118586187795713</v>
+        <v>0.1255333557085</v>
       </c>
       <c r="G13" t="s">
         <v>11</v>
@@ -746,19 +749,19 @@
         <v>21</v>
       </c>
       <c r="B14" t="n">
-        <v>0.864656101622476</v>
+        <v>1.19707001886912</v>
       </c>
       <c r="C14" t="n">
-        <v>3.27531478684193</v>
+        <v>1.69653064629389</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0172931220324495</v>
+        <v>0.0239414003773824</v>
       </c>
       <c r="E14" t="n">
-        <v>413.765739342097</v>
+        <v>334.826532314694</v>
       </c>
       <c r="F14" t="n">
-        <v>0.149217740568832</v>
+        <v>0.118342732107112</v>
       </c>
       <c r="G14" t="s">
         <v>11</v>
@@ -769,19 +772,19 @@
         <v>22</v>
       </c>
       <c r="B15" t="n">
-        <v>1.58660335375993</v>
+        <v>1.01689224832455</v>
       </c>
       <c r="C15" t="n">
-        <v>3.828365071639</v>
+        <v>2.86425015471777</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0317320670751987</v>
+        <v>0.020337844966491</v>
       </c>
       <c r="E15" t="n">
-        <v>441.41825358195</v>
+        <v>393.212507735888</v>
       </c>
       <c r="F15" t="n">
-        <v>0.165681114601585</v>
+        <v>0.158065373745723</v>
       </c>
       <c r="G15" t="s">
         <v>11</v>
@@ -792,19 +795,19 @@
         <v>23</v>
       </c>
       <c r="B16" t="n">
-        <v>0.478745215985887</v>
+        <v>1.84274165364575</v>
       </c>
       <c r="C16" t="n">
-        <v>3.41892021911421</v>
+        <v>3.32939325342833</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00957490431971774</v>
+        <v>0.0368548330729151</v>
       </c>
       <c r="E16" t="n">
-        <v>420.94601095571</v>
+        <v>416.469662671417</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0883300542486196</v>
+        <v>0.16643587713991</v>
       </c>
       <c r="G16" t="s">
         <v>11</v>
@@ -815,19 +818,19 @@
         <v>24</v>
       </c>
       <c r="B17" t="n">
-        <v>1.34868030267701</v>
+        <v>0.527649752206104</v>
       </c>
       <c r="C17" t="n">
-        <v>3.31778542533145</v>
+        <v>2.9422510997939</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0269736060535403</v>
+        <v>0.0105529950441221</v>
       </c>
       <c r="E17" t="n">
-        <v>415.889271266572</v>
+        <v>397.112554989695</v>
       </c>
       <c r="F17" t="n">
-        <v>0.244027280290688</v>
+        <v>0.0830929411150078</v>
       </c>
       <c r="G17" t="s">
         <v>11</v>
@@ -838,19 +841,19 @@
         <v>25</v>
       </c>
       <c r="B18" t="n">
-        <v>1.62156198903047</v>
+        <v>1.60501742434143</v>
       </c>
       <c r="C18" t="n">
-        <v>2.83763187369344</v>
+        <v>2.88845732787593</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0324312397806094</v>
+        <v>0.0321003484868285</v>
       </c>
       <c r="E18" t="n">
-        <v>391.881593684672</v>
+        <v>394.422866393796</v>
       </c>
       <c r="F18" t="n">
-        <v>0.166576984043539</v>
+        <v>0.248057358405895</v>
       </c>
       <c r="G18" t="s">
         <v>11</v>
@@ -861,19 +864,19 @@
         <v>26</v>
       </c>
       <c r="B19" t="n">
-        <v>2.46170027267156</v>
+        <v>1.84595393409254</v>
       </c>
       <c r="C19" t="n">
-        <v>2.4054463568768</v>
+        <v>2.47962246500893</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0492340054534311</v>
+        <v>0.0369190786818508</v>
       </c>
       <c r="E19" t="n">
-        <v>370.27231784384</v>
+        <v>373.981123250447</v>
       </c>
       <c r="F19" t="n">
-        <v>0.188459040238128</v>
+        <v>0.169616369397473</v>
       </c>
       <c r="G19" t="s">
         <v>11</v>
@@ -884,19 +887,19 @@
         <v>27</v>
       </c>
       <c r="B20" t="n">
-        <v>1.79149491710978</v>
+        <v>2.81213758005362</v>
       </c>
       <c r="C20" t="n">
-        <v>2.16819183133219</v>
+        <v>2.10122290575614</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0358298983421955</v>
+        <v>0.0562427516010724</v>
       </c>
       <c r="E20" t="n">
-        <v>358.40959156661</v>
+        <v>355.061145287807</v>
       </c>
       <c r="F20" t="n">
-        <v>0.134022867321996</v>
+        <v>0.192321125988655</v>
       </c>
       <c r="G20" t="s">
         <v>11</v>
@@ -907,19 +910,19 @@
         <v>28</v>
       </c>
       <c r="B21" t="n">
-        <v>1.09957922332884</v>
+        <v>1.95163830744445</v>
       </c>
       <c r="C21" t="n">
-        <v>2.89593852746767</v>
+        <v>1.85934840042381</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0219915844665768</v>
+        <v>0.039032766148889</v>
       </c>
       <c r="E21" t="n">
-        <v>394.796926373384</v>
+        <v>342.967420021191</v>
       </c>
       <c r="F21" t="n">
-        <v>0.224422000574448</v>
+        <v>0.132467436743443</v>
       </c>
       <c r="G21" t="s">
         <v>11</v>
@@ -930,19 +933,19 @@
         <v>29</v>
       </c>
       <c r="B22" t="n">
-        <v>1.76838321535747</v>
+        <v>1.24600407436677</v>
       </c>
       <c r="C22" t="n">
-        <v>2.46807820805403</v>
+        <v>2.51720523013369</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0353676643071494</v>
+        <v>0.0249200814873353</v>
       </c>
       <c r="E22" t="n">
-        <v>373.403910402701</v>
+        <v>375.860261506684</v>
       </c>
       <c r="F22" t="n">
-        <v>0.159246532165181</v>
+        <v>0.226747050951325</v>
       </c>
       <c r="G22" t="s">
         <v>11</v>
@@ -953,19 +956,19 @@
         <v>30</v>
       </c>
       <c r="B23" t="n">
-        <v>1.55444022893458</v>
+        <v>1.98121646697375</v>
       </c>
       <c r="C23" t="n">
-        <v>2.49874431048931</v>
+        <v>2.15134938066146</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0310888045786916</v>
+        <v>0.039624329339475</v>
       </c>
       <c r="E23" t="n">
-        <v>374.937215524465</v>
+        <v>357.567469033073</v>
       </c>
       <c r="F23" t="n">
-        <v>0.151249326502043</v>
+        <v>0.162451003015797</v>
       </c>
       <c r="G23" t="s">
         <v>11</v>
@@ -976,19 +979,19 @@
         <v>31</v>
       </c>
       <c r="B24" t="n">
-        <v>0.269236345015944</v>
+        <v>1.73132134739972</v>
       </c>
       <c r="C24" t="n">
-        <v>4.12702385973277</v>
+        <v>2.17523169728017</v>
       </c>
       <c r="D24" t="n">
-        <v>0.00538472690031889</v>
+        <v>0.0346264269479944</v>
       </c>
       <c r="E24" t="n">
-        <v>456.351192986638</v>
+        <v>358.761584864008</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0440545277271453</v>
+        <v>0.153820425323923</v>
       </c>
       <c r="G24" t="s">
         <v>11</v>
@@ -999,22 +1002,22 @@
         <v>32</v>
       </c>
       <c r="B25" t="n">
-        <v>2.85</v>
+        <v>0.300247083831795</v>
       </c>
       <c r="C25" t="n">
-        <v>2.35786</v>
+        <v>3.60018450162607</v>
       </c>
       <c r="D25" t="n">
-        <v>0.057</v>
+        <v>0.0060049416766359</v>
       </c>
       <c r="E25" t="n">
-        <v>367.893</v>
+        <v>430.009225081303</v>
       </c>
       <c r="F25" t="n">
-        <v>0.156</v>
+        <v>0.0441663572344428</v>
       </c>
       <c r="G25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26">
@@ -1022,21 +1025,44 @@
         <v>33</v>
       </c>
       <c r="B26" t="n">
-        <v>1.40498967035606</v>
+        <v>2.85</v>
       </c>
       <c r="C26" t="n">
-        <v>2.51399798875245</v>
+        <v>2.35786</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0280997934071211</v>
+        <v>0.057</v>
       </c>
       <c r="E26" t="n">
-        <v>375.699899437622</v>
+        <v>367.893</v>
       </c>
       <c r="F26" t="n">
-        <v>0.15595897164757</v>
+        <v>0.156</v>
       </c>
       <c r="G26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1.5341214625056</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2.18105819723049</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.030682429250112</v>
+      </c>
+      <c r="E27" t="n">
+        <v>359.052909861525</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.155858756228296</v>
+      </c>
+      <c r="G27" t="s">
         <v>11</v>
       </c>
     </row>
